--- a/ATSBR/avgts_dd.xlsx
+++ b/ATSBR/avgts_dd.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philliao/Downloads/Code/IB-Math-IA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philliao/Downloads/Code/IB-Math-IA/ATSBR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED909ACB-AAA8-8142-907A-BE10C3031EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C2BF8C-3BFB-6B4E-8DBD-85035352D88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="660" windowWidth="21760" windowHeight="14320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Generate a table for Attributes" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="52">
   <si>
     <t>Attribute Name</t>
   </si>
@@ -140,13 +140,49 @@
   </si>
   <si>
     <t>https://opendata.actransit.org/dataset/general-transit-feed-specification-gtfs/resource/6aca1be0-dfea-485e-b859-b3303fc6eb36?inner_span=True</t>
+  </si>
+  <si>
+    <t>Before Modification Name</t>
+  </si>
+  <si>
+    <t>After Modification Name</t>
+  </si>
+  <si>
+    <t>After Modification Meaning</t>
+  </si>
+  <si>
+    <t>speed_cr</t>
+  </si>
+  <si>
+    <t>Congestion rate at the specific location</t>
+  </si>
+  <si>
+    <t>district_Shape_Length</t>
+  </si>
+  <si>
+    <t>shape_Length</t>
+  </si>
+  <si>
+    <t>Agregate total weight of each district</t>
+  </si>
+  <si>
+    <t>district_congestion_index</t>
+  </si>
+  <si>
+    <t>Agregate congestion rate of the district</t>
+  </si>
+  <si>
+    <t>speed_acr</t>
+  </si>
+  <si>
+    <t>/No change of meaning</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -178,13 +214,38 @@
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
+        <bgColor rgb="FFF6F8F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF356854"/>
+        <bgColor rgb="FF356854"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="12">
@@ -364,7 +425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -411,6 +472,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -675,10 +755,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="37.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.1640625" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
@@ -979,6 +1060,66 @@
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="20"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="1">
